--- a/data/sources/countries/uruguay.xlsx
+++ b/data/sources/countries/uruguay.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI33"/>
+  <dimension ref="A1:BE33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -827,7 +731,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -865,12 +769,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Construcción de línea de alta tensión entre Tacuarembó y Salto</t>
+          <t>Construcción De Línea De Alta Tensión Entre Tacuarembó Y Salto</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>construction of high-voltage transmission line between Tacuarembó and Salto</t>
+          <t>Construction Of High-Voltage Transmission Line Between Tacuarembó And Salto</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -906,33 +810,23 @@
           <t>https://latsustentable.org/wp-content/uploads/2024/05/IFR_Suramerica_FINAL-2024mayo.pdf#page=126</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Latinoamérica Sustentable and Sustense. (2024). “A diez años de la Iniciativa de la Franja y la Ruta:Desafíos ambientales y sociales de las inversiones de China en América del Sur,” Latinoamérica Sustentable and Sustense, 2024.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>https://latsustentable.org/wp-content/uploads/2024/05/IFR\_Suramerica\_FINAL-2024mayo.pdf\#page=126</t>
-        </is>
-      </c>
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -965,7 +859,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1003,12 +897,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Construcción de línea de alta tensión entre Tacuarembó y Salto</t>
+          <t>Construcción De Línea De Alta Tensión Entre Tacuarembó Y Salto</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>construction of high-voltage transmission line between Tacuarembó and Salto</t>
+          <t>Construction Of High-Voltage Transmission Line Between Tacuarembó And Salto</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1026,41 +920,31 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Latinoamérica Sustentable and Sustense. (2024). “A diez años de la Iniciativa de la Franja y la Ruta:Desafíos ambientales y sociales de las inversiones de China en América del Sur,” Latinoamérica Sustentable and Sustense, 2024.</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>https://latsustentable.org/wp-content/uploads/2024/05/IFR\_Suramerica\_FINAL-2024mayo.pdf\#page=126</t>
         </is>
       </c>
       <c r="BA3" t="n">
         <v>4</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -1093,7 +977,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1131,12 +1015,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Construcción de línea de alta tensión entre Tacuarembó y Salto</t>
+          <t>Construcción De Línea De Alta Tensión Entre Tacuarembó Y Salto</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>construction of high-voltage transmission line between Tacuarembó and Salto</t>
+          <t>Construction Of High-Voltage Transmission Line Between Tacuarembó And Salto</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1154,41 +1038,31 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Latinoamérica Sustentable and Sustense. (2024). “A diez años de la Iniciativa de la Franja y la Ruta:Desafíos ambientales y sociales de las inversiones de China en América del Sur,” Latinoamérica Sustentable and Sustense, 2024.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>https://latsustentable.org/wp-content/uploads/2024/05/IFR\_Suramerica\_FINAL-2024mayo.pdf\#page=126</t>
         </is>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -1221,7 +1095,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1259,12 +1133,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Centro de distribución regional</t>
+          <t>Centro De Distribución Regional</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Regional distribution center</t>
+          <t>Regional Distribution Center</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1293,20 +1167,15 @@
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>Confirmado: LiuGong Machinery inauguró centro de distribución regional en Zonamerica, Montevideo (no en el centro de Montevideo). El año exacto no es totalmente claro en las fuentes (la entrada dice 2014, el artículo de Transporte Carretero lo confirma como inaugurado en Parque de las Ciencias, Canelones). El monto de USD 3M es plausible para un centro de distribución de repuestos.</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>https://www.transportecarretero.com.uy/noticias/maquinaria/compania-china-liugong-instalo-centro-de-distribucion-en-uruguay.html</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>https://panjiva.com/Liugong-Machinery-Uruguay-SA/42425516</t>
         </is>
@@ -1339,7 +1208,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1421,25 +1290,20 @@
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>El laboratorio clinico de BGI Genomics en Uruguay inaugurado en 2024 esta confirmado por la web oficial de BGI, Yahoo Finance y Uruguay XXI (agencia gubernamental de inversiones). La inversion inicial es de USD 10M con compromisos de hasta USD 45M en cinco anos.</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://www.bgi.com/global/news/bgi-genomics-unveils-first-cutting-edge-clinical-lab-in-uruguay</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bgi-genomics-leads-innovation-inaugural-002700935.html</t>
+        </is>
+      </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://www.bgi.com/global/news/bgi-genomics-unveils-first-cutting-edge-clinical-lab-in-uruguay</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/news/bgi-genomics-leads-innovation-inaugural-002700935.html</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/en/news/article/leading-chinese-company-in-human-genetics-diagnostics-set-up-its-first-laboratory-in-latin-america-in-uruguay/</t>
         </is>
@@ -1472,7 +1336,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1510,12 +1374,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Planta de producción de suero bovino</t>
+          <t>Planta De Producción De Suero Bovino</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bovine serum production plant</t>
+          <t>Bovine Serum Production Plant</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1544,20 +1408,15 @@
       <c r="BA7" t="n">
         <v>3</v>
       </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>La inauguracion de la planta ARTICA BIOTECH de ExCell Bio en Zonamerica, Uruguay en abril de 2023 esta confirmada por la empresa y medios secundarios. Existe ambiguedad sobre cual planta corresponde al registro pues hay referencia a una inversion previa de USD 20M en 2021.</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>0</v>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>http://www.excellbio.com/en/companynews/info.aspx?itemid=2310</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>https://www.excell-artica.com/news/excellbio-honored-on-forbes-list-a-decade-of-dedication-leads-to-breakthrough-success.html</t>
         </is>
@@ -1587,7 +1446,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1602,7 +1461,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Unidentified</t>
+          <t>CMEC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1630,7 +1489,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1656,23 +1515,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1</v>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
       </c>
       <c r="BD8" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -1702,7 +1550,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1745,7 +1593,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1771,23 +1619,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1</v>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
       </c>
       <c r="BD9" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -1817,7 +1654,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1860,7 +1697,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1886,23 +1723,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1</v>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692524</t>
+        </is>
       </c>
       <c r="BD10" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692524</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -1932,7 +1758,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -1975,7 +1801,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2001,23 +1827,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1</v>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692525</t>
+        </is>
       </c>
       <c r="BD11" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692525</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2047,7 +1862,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2090,7 +1905,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2116,23 +1931,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1</v>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692526</t>
+        </is>
       </c>
       <c r="BD12" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692526</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2162,7 +1966,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2205,7 +2009,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2231,23 +2035,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1</v>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692527</t>
+        </is>
       </c>
       <c r="BD13" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692527</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2277,7 +2070,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2320,7 +2113,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2346,23 +2139,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1</v>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692528</t>
+        </is>
       </c>
       <c r="BD14" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692528</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2392,7 +2174,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2435,7 +2217,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2461,23 +2243,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1</v>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692529</t>
+        </is>
       </c>
       <c r="BD15" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692529</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2507,7 +2278,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2550,7 +2321,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2576,23 +2347,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1</v>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692530</t>
+        </is>
       </c>
       <c r="BD16" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692530</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2622,7 +2382,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2665,7 +2425,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2691,23 +2451,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1</v>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692531</t>
+        </is>
       </c>
       <c r="BD17" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692531</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2737,7 +2486,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2780,7 +2529,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2806,23 +2555,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1</v>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692532</t>
+        </is>
       </c>
       <c r="BD18" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692532</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2852,7 +2590,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -2895,7 +2633,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2921,23 +2659,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1</v>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692533</t>
+        </is>
       </c>
       <c r="BD19" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692533</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -2967,7 +2694,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3010,7 +2737,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3036,23 +2763,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1</v>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692534</t>
+        </is>
       </c>
       <c r="BD20" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692534</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3082,7 +2798,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3125,7 +2841,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3151,23 +2867,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1</v>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692535</t>
+        </is>
       </c>
       <c r="BD21" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692535</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3197,7 +2902,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3240,7 +2945,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3266,23 +2971,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1</v>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692536</t>
+        </is>
       </c>
       <c r="BD22" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692536</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3312,7 +3006,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3355,7 +3049,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3381,23 +3075,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1</v>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692537</t>
+        </is>
       </c>
       <c r="BD23" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692537</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3427,7 +3110,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3470,7 +3153,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3496,23 +3179,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1</v>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692538</t>
+        </is>
       </c>
       <c r="BD24" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692538</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3542,7 +3214,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3585,7 +3257,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3611,23 +3283,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA25" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1</v>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692539</t>
+        </is>
       </c>
       <c r="BD25" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692539</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3657,7 +3318,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3700,7 +3361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3726,23 +3387,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA26" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1</v>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692540</t>
+        </is>
       </c>
       <c r="BD26" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692540</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3772,7 +3422,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3815,7 +3465,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3841,23 +3491,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1</v>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692541</t>
+        </is>
       </c>
       <c r="BD27" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692541</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -3887,7 +3526,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -3930,7 +3569,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3956,23 +3595,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA28" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1</v>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692542</t>
+        </is>
       </c>
       <c r="BD28" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692542</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -4002,7 +3630,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -4045,7 +3673,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4071,23 +3699,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1</v>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692543</t>
+        </is>
       </c>
       <c r="BD29" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692543</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -4117,7 +3734,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -4160,7 +3777,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4186,23 +3803,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA30" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1</v>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692544</t>
+        </is>
       </c>
       <c r="BD30" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692544</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -4232,7 +3838,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -4275,7 +3881,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4301,23 +3907,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1</v>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692545</t>
+        </is>
       </c>
       <c r="BD31" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692545</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -4347,7 +3942,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -4390,7 +3985,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4416,23 +4011,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1</v>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692546</t>
+        </is>
       </c>
       <c r="BD32" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692546</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
@@ -4462,7 +4046,7 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>858</t>
         </is>
@@ -4505,7 +4089,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE. Largest work in the Uruguayan power system for the five-year period.</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4531,23 +4115,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1</v>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692547</t>
+        </is>
       </c>
       <c r="BD33" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692547</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>

--- a/data/sources/countries/uruguay.xlsx
+++ b/data/sources/countries/uruguay.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE33"/>
+  <dimension ref="A1:BG33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -731,10 +740,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G2" t="n">
+        <v>858</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -785,6 +792,9 @@
       <c r="R2" t="n">
         <v>200</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -810,23 +820,51 @@
           <t>https://latsustentable.org/wp-content/uploads/2024/05/IFR_Suramerica_FINAL-2024mayo.pdf#page=126</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -859,10 +897,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G3" t="n">
+        <v>858</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -913,6 +949,9 @@
       <c r="R3" t="n">
         <v>200</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -928,23 +967,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>4</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -977,10 +1046,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G4" t="n">
+        <v>858</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1031,6 +1098,9 @@
       <c r="R4" t="n">
         <v>200</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1046,23 +1116,53 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.marketscreener.com/quote/stock/CHINA-MACHINERY-ENGINEERI-12212398/news/China-Machinery-Engineering-CMEC-Signs-Contract-for-Uruguay-s-500kV-Power-Transmission-and-Transfo-35533509/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202106/t20210610_293483.html</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.business-humanrights.org/en/latest-news/china-machinery-engineering-corporation-cmec-non-response-re-alleged-abuse-of-workers-constructing-transmission-line/</t>
         </is>
@@ -1095,10 +1195,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G5" t="n">
+        <v>858</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1149,6 +1247,9 @@
       <c r="R5" t="n">
         <v>3</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1164,22 +1265,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Confirmado: LiuGong Machinery inauguró centro de distribución regional en Zonamerica, Montevideo (no en el centro de Montevideo). El año exacto no es totalmente claro en las fuentes (la entrada dice 2014, el artículo de Transporte Carretero lo confirma como inaugurado en Parque de las Ciencias, Canelones). El monto de USD 3M es plausible para un centro de distribución de repuestos.</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://www.transportecarretero.com.uy/noticias/maquinaria/compania-china-liugong-instalo-centro-de-distribucion-en-uruguay.html</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://panjiva.com/Liugong-Machinery-Uruguay-SA/42425516</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1208,10 +1344,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G6" t="n">
+        <v>858</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1262,6 +1396,9 @@
       <c r="R6" t="n">
         <v>10</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1287,23 +1424,55 @@
           <t>https://search.informit.org/doi/epdf/10.3316/informit.T2024051500023690262139776</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>El laboratorio clinico de BGI Genomics en Uruguay inaugurado en 2024 esta confirmado por la web oficial de BGI, Yahoo Finance y Uruguay XXI (agencia gubernamental de inversiones). La inversion inicial es de USD 10M con compromisos de hasta USD 45M en cinco anos.</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://www.bgi.com/global/news/bgi-genomics-unveils-first-cutting-edge-clinical-lab-in-uruguay</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://finance.yahoo.com/news/bgi-genomics-leads-innovation-inaugural-002700935.html</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/en/news/article/leading-chinese-company-in-human-genetics-diagnostics-set-up-its-first-laboratory-in-latin-america-in-uruguay/</t>
         </is>
@@ -1336,10 +1505,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G7" t="n">
+        <v>858</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1390,6 +1557,9 @@
       <c r="R7" t="n">
         <v>10</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -1405,22 +1575,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>3</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>La inauguracion de la planta ARTICA BIOTECH de ExCell Bio en Zonamerica, Uruguay en abril de 2023 esta confirmada por la empresa y medios secundarios. Existe ambiguedad sobre cual planta corresponde al registro pues hay referencia a una inversion previa de USD 20M en 2021.</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>http://www.excellbio.com/en/companynews/info.aspx?itemid=2310</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://www.excell-artica.com/news/excellbio-honored-on-forbes-list-a-decade-of-dedication-leads-to-breakthrough-success.html</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1428,6 +1633,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>2</v>
       </c>
@@ -1446,10 +1652,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G8" t="n">
+        <v>858</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1500,6 +1704,9 @@
       <c r="R8" t="n">
         <v>170</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1515,16 +1722,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1532,6 +1780,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2</v>
       </c>
@@ -1550,10 +1799,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G9" t="n">
+        <v>858</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1604,6 +1851,9 @@
       <c r="R9" t="n">
         <v>170</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1619,16 +1869,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1636,6 +1927,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>2</v>
       </c>
@@ -1654,10 +1946,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G10" t="n">
+        <v>858</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1708,6 +1998,9 @@
       <c r="R10" t="n">
         <v>170</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1723,16 +2016,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692524</t>
-        </is>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>1</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1740,6 +2074,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>2</v>
       </c>
@@ -1758,10 +2093,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G11" t="n">
+        <v>858</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1812,6 +2145,9 @@
       <c r="R11" t="n">
         <v>170</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1827,16 +2163,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692525</t>
-        </is>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>1</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1844,6 +2221,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>2</v>
       </c>
@@ -1862,10 +2240,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G12" t="n">
+        <v>858</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1916,6 +2292,9 @@
       <c r="R12" t="n">
         <v>170</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1931,16 +2310,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692526</t>
-        </is>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>1</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1948,6 +2368,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>2</v>
       </c>
@@ -1966,10 +2387,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G13" t="n">
+        <v>858</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2020,6 +2439,9 @@
       <c r="R13" t="n">
         <v>170</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2035,16 +2457,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692527</t>
-        </is>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>1</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2052,6 +2515,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>2</v>
       </c>
@@ -2070,10 +2534,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G14" t="n">
+        <v>858</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2124,6 +2586,9 @@
       <c r="R14" t="n">
         <v>170</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2139,16 +2604,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692528</t>
-        </is>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>1</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2156,6 +2662,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>2</v>
       </c>
@@ -2174,10 +2681,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G15" t="n">
+        <v>858</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2228,6 +2733,9 @@
       <c r="R15" t="n">
         <v>170</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2243,16 +2751,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692529</t>
-        </is>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>1</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2260,6 +2809,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2</v>
       </c>
@@ -2278,10 +2828,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G16" t="n">
+        <v>858</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2332,6 +2880,9 @@
       <c r="R16" t="n">
         <v>170</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2347,16 +2898,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692530</t>
-        </is>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>1</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2364,6 +2956,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>2</v>
       </c>
@@ -2382,10 +2975,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G17" t="n">
+        <v>858</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2436,6 +3027,9 @@
       <c r="R17" t="n">
         <v>170</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2451,16 +3045,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692531</t>
-        </is>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
+        <v>1</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2468,6 +3103,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>2</v>
       </c>
@@ -2486,10 +3122,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G18" t="n">
+        <v>858</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2540,6 +3174,9 @@
       <c r="R18" t="n">
         <v>170</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2555,16 +3192,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692532</t>
-        </is>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
+        <v>1</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2572,6 +3250,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>2</v>
       </c>
@@ -2590,10 +3269,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G19" t="n">
+        <v>858</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2644,6 +3321,9 @@
       <c r="R19" t="n">
         <v>170</v>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2659,16 +3339,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692533</t>
-        </is>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
+        <v>1</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2676,6 +3397,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>2</v>
       </c>
@@ -2694,10 +3416,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G20" t="n">
+        <v>858</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2748,6 +3468,9 @@
       <c r="R20" t="n">
         <v>170</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2763,16 +3486,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692534</t>
-        </is>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
+        <v>1</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2780,6 +3544,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>2</v>
       </c>
@@ -2798,10 +3563,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G21" t="n">
+        <v>858</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2852,6 +3615,9 @@
       <c r="R21" t="n">
         <v>170</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2867,16 +3633,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692535</t>
-        </is>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
+        <v>1</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2884,6 +3691,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>2</v>
       </c>
@@ -2902,10 +3710,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G22" t="n">
+        <v>858</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2956,6 +3762,9 @@
       <c r="R22" t="n">
         <v>170</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2971,16 +3780,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692536</t>
-        </is>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
+        <v>1</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2988,6 +3838,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>2</v>
       </c>
@@ -3006,10 +3857,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G23" t="n">
+        <v>858</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3060,6 +3909,9 @@
       <c r="R23" t="n">
         <v>170</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3075,16 +3927,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692537</t>
-        </is>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="n">
+        <v>1</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3092,6 +3985,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>2</v>
       </c>
@@ -3110,10 +4004,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G24" t="n">
+        <v>858</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3164,6 +4056,9 @@
       <c r="R24" t="n">
         <v>170</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3179,16 +4074,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692538</t>
-        </is>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="n">
+        <v>1</v>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3196,6 +4132,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>2</v>
       </c>
@@ -3214,10 +4151,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G25" t="n">
+        <v>858</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3268,6 +4203,9 @@
       <c r="R25" t="n">
         <v>170</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3283,16 +4221,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692539</t>
-        </is>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="n">
+        <v>1</v>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3300,6 +4279,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>2</v>
       </c>
@@ -3318,10 +4298,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G26" t="n">
+        <v>858</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3372,6 +4350,9 @@
       <c r="R26" t="n">
         <v>170</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3387,16 +4368,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692540</t>
-        </is>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="n">
+        <v>1</v>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3404,6 +4426,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>2</v>
       </c>
@@ -3422,10 +4445,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G27" t="n">
+        <v>858</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3476,6 +4497,9 @@
       <c r="R27" t="n">
         <v>170</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3491,16 +4515,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC27" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692541</t>
-        </is>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
+        <v>1</v>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3508,6 +4573,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>2</v>
       </c>
@@ -3526,10 +4592,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G28" t="n">
+        <v>858</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3580,6 +4644,9 @@
       <c r="R28" t="n">
         <v>170</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3595,16 +4662,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692542</t>
-        </is>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
+        <v>1</v>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3612,6 +4720,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>2</v>
       </c>
@@ -3630,10 +4739,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G29" t="n">
+        <v>858</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3684,6 +4791,9 @@
       <c r="R29" t="n">
         <v>170</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3699,16 +4809,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC29" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692543</t>
-        </is>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="n">
+        <v>1</v>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3716,6 +4867,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>2</v>
       </c>
@@ -3734,10 +4886,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G30" t="n">
+        <v>858</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3788,6 +4938,9 @@
       <c r="R30" t="n">
         <v>170</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3803,16 +4956,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692544</t>
-        </is>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="n">
+        <v>1</v>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3820,6 +5014,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>2</v>
       </c>
@@ -3838,10 +5033,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G31" t="n">
+        <v>858</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3892,6 +5085,9 @@
       <c r="R31" t="n">
         <v>170</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3907,16 +5103,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692545</t>
-        </is>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="n">
+        <v>1</v>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3924,6 +5161,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>2</v>
       </c>
@@ -3942,10 +5180,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G32" t="n">
+        <v>858</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3996,6 +5232,9 @@
       <c r="R32" t="n">
         <v>170</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4011,16 +5250,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692546</t>
-        </is>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="n">
+        <v>1</v>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4028,6 +5308,7 @@
           <t>URY-0002</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>2</v>
       </c>
@@ -4046,10 +5327,8 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
+      <c r="G33" t="n">
+        <v>858</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4100,6 +5379,9 @@
       <c r="R33" t="n">
         <v>170</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4115,16 +5397,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692547</t>
-        </is>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="n">
+        <v>1</v>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>https://www.montevideo.com.uy/Noticias/Uruguay-firma-acuerdo-para-atraer-inversion-china-en-infraestructuras-uc692523</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
           <t>https://www.uruguayxxi.gub.uy/es/noticias/articulo/uruguay-impulsa-su-insercion-internacional-con-una-mision-oficial-a-china/</t>
         </is>
       </c>
+      <c r="BG33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sources/countries/uruguay.xlsx
+++ b/data/sources/countries/uruguay.xlsx
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility UTE</t>
+          <t>Closure of the 500 kV transmission ring: 365 km of line linking Tacuarembo, Salto and Chamberlain for the state utility.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
